--- a/excel-files/CALOOCAN/ANTONIO LUNA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/ANTONIO LUNA ELEMENTARY SCHOOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="738" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27FBA279-D2BE-4050-95EE-65B0261EB35B}"/>
+  <xr:revisionPtr revIDLastSave="803" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCCEACB5-DF0F-4653-9CAE-102F6CD55EE1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -6029,15 +6029,12 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E81:E89 E71:E79 E51:E59 E61:E69" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E81:E89 E71:E79 E51:E59 E61:E69" xr:uid="{1D5D38AA-FB7D-4EF2-BB04-F66B17D70DAF}">
-      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15438,18 +15435,21 @@
     <mergeCell ref="V1:AA1"/>
     <mergeCell ref="AB1:AG1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y112:Y127 S112:S127 AE112:AE127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD23:AD31 AD33:AD41 AD43:AD51 AD63:AD71 AD73:AD81 AD53:AD61 R112:R127 AD83:AD91 AD93:AD101 AD14:AD21 AD5:AD12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 X112:X127 R83:R91 R93:R101 R14:R21 R5:R12 X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 AD112:AD127 X83:X91 X93:X101 X14:X21 X5:X12 AD103:AD110 X103:X110 R103:R110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD112:AD127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S14:S110 AE14:AE110 Y4:Y110 G5:G12 S5:S12 AE5:AE12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127" xr:uid="{3F60B684-BFA8-4E98-9C1A-39BEC70F89D1}">
       <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110 X112:X127 AD5:AD12 AD14:AD21 AD23:AD31 AD33:AD41 AD43:AD51 AD53:AD61 AD63:AD71 AD73:AD81 AD83:AD91 AD93:AD101 AD103:AD110" xr:uid="{36DA126B-1515-45EC-8E5D-2FB00D9335DB}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24863,15 +24863,21 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S131:S138 Y131:Y138 G131:G138 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M83:M93 G83:G93 Y83:Y93 S83:S93 S95:S105 M95:M105 G95:G105 Y95:Y105 Y107:Y117 S107:S117 M107:M117 G107:G117 G119:G129 Y119:Y129 S119:S129 M119:M129 M131:M138" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X83:X93 X95:X105 X55:X65 X107:X117 X119:X129 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L83:L93 L95:L105 L55:L65 L107:L117 L119:L129 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R83:R93 R95:R105 R55:R65 R107:R117 R119:R129 R12:R19 R3:R10 X131:X138 R131:R138 L131:L138" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R107:R117 R83:R93 R131:R138 R119:R129 R95:R105" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F43:F53 F31:F41 F21:F29 F3:F10 F12:F19 F55:F65 F119:F129 F107:F117 F83:F93 F95:F105 F131:F138" xr:uid="{752A108F-029B-4153-A03C-5205FDE9F713}">
       <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L83:L93 L95:L105 L107:L117 L119:L129 L131:L138 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65" xr:uid="{D5BFE704-B8AF-46B2-A02D-47497766968A}">
+      <formula1>"2024,2025 ,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X83:X93 X95:X105 X107:X117 X119:X129 X131:X138" xr:uid="{AA4D75E5-3473-4C99-8D57-36407E8E9B8D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
